--- a/data/trans_dic/P23_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 36,98</t>
+          <t>31,21; 37,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,97; 35,45</t>
+          <t>29,33; 35,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,53; 33,15</t>
+          <t>26,51; 32,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,76; 31,53</t>
+          <t>23,47; 31,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 15,08</t>
+          <t>11,24; 14,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,86</t>
+          <t>12,77; 16,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 16,0</t>
+          <t>11,51; 16,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 12,35</t>
+          <t>8,88; 12,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 24,34</t>
+          <t>20,66; 24,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,42; 24,08</t>
+          <t>20,31; 23,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 22,53</t>
+          <t>18,55; 22,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,53; 19,05</t>
+          <t>15,47; 19,21</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,96; 47,74</t>
+          <t>42,91; 47,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,07; 42,54</t>
+          <t>38,12; 42,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,77; 41,04</t>
+          <t>36,65; 41,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 29,69</t>
+          <t>18,81; 29,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,09; 35,79</t>
+          <t>31,22; 35,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,25; 37,69</t>
+          <t>33,22; 38,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 35,2</t>
+          <t>31,14; 35,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,44; 24,18</t>
+          <t>15,75; 24,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,88; 41,34</t>
+          <t>37,94; 41,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 39,6</t>
+          <t>36,46; 39,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,72; 37,64</t>
+          <t>34,62; 37,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,13; 26,26</t>
+          <t>18,58; 26,26</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,4; 37,42</t>
+          <t>29,71; 38,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,21; 37,6</t>
+          <t>28,6; 37,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 28,94</t>
+          <t>21,14; 29,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,79; 20,27</t>
+          <t>13,0; 20,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,53; 31,09</t>
+          <t>22,79; 30,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,52; 34,46</t>
+          <t>25,43; 34,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 25,46</t>
+          <t>18,51; 25,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 19,03</t>
+          <t>13,77; 19,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 33,56</t>
+          <t>27,3; 33,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,0; 34,37</t>
+          <t>27,59; 34,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,98; 26,32</t>
+          <t>20,85; 26,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,03</t>
+          <t>14,27; 18,67</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,0; 41,57</t>
+          <t>38,25; 41,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,06; 38,44</t>
+          <t>35,1; 38,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,91; 36,14</t>
+          <t>32,9; 36,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,1; 26,86</t>
+          <t>18,67; 26,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 26,21</t>
+          <t>23,11; 25,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 28,55</t>
+          <t>25,51; 28,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,5; 27,52</t>
+          <t>24,44; 27,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,68</t>
+          <t>14,82; 19,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,89; 33,31</t>
+          <t>30,93; 33,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,62; 33,09</t>
+          <t>30,64; 32,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 31,27</t>
+          <t>28,95; 31,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,61</t>
+          <t>18,07; 22,51</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>320323; 381175</t>
+          <t>321721; 381632</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>282391; 345543</t>
+          <t>285881; 344073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199866; 249807</t>
+          <t>199745; 248570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122350; 162353</t>
+          <t>120868; 161940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>150155; 198271</t>
+          <t>147783; 195295</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>172023; 225606</t>
+          <t>170834; 222476</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>116721; 158762</t>
+          <t>114211; 159950</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67444; 93320</t>
+          <t>67092; 91988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>487779; 571051</t>
+          <t>484580; 565242</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>472297; 556850</t>
+          <t>469586; 550576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>327104; 393330</t>
+          <t>323901; 394300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>197344; 242002</t>
+          <t>196478; 244067</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>727420; 808445</t>
+          <t>726712; 811865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>747368; 834994</t>
+          <t>748262; 831825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>763425; 852246</t>
+          <t>761085; 853057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406821; 679419</t>
+          <t>430492; 679356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>493534; 568151</t>
+          <t>495661; 568206</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>583770; 661822</t>
+          <t>583198; 670806</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>620480; 699211</t>
+          <t>618596; 701404</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>345271; 540677</t>
+          <t>352286; 537096</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1242956; 1356544</t>
+          <t>1244972; 1356350</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1348676; 1472770</t>
+          <t>1355763; 1472522</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1410542; 1529293</t>
+          <t>1406342; 1531101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>865553; 1188253</t>
+          <t>840496; 1188248</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>162131; 206310</t>
+          <t>163797; 209809</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135761; 180922</t>
+          <t>137596; 180937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115929; 157933</t>
+          <t>115378; 158574</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82710; 131050</t>
+          <t>84075; 133102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>107359; 148093</t>
+          <t>108580; 145905</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>117054; 158049</t>
+          <t>116620; 158387</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100239; 139570</t>
+          <t>101448; 140069</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91502; 125185</t>
+          <t>90574; 125348</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>284861; 344952</t>
+          <t>280573; 342402</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>263191; 322982</t>
+          <t>259269; 321209</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229525; 287983</t>
+          <t>228087; 288264</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>187542; 248201</t>
+          <t>186162; 243512</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1244842; 1361477</t>
+          <t>1252736; 1365380</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1198467; 1314057</t>
+          <t>1200043; 1314908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1110958; 1220029</t>
+          <t>1110754; 1221694</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>658818; 926608</t>
+          <t>644246; 916288</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>785050; 885840</t>
+          <t>781070; 876985</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>905566; 1014150</t>
+          <t>906191; 1014851</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>864180; 970567</t>
+          <t>861760; 970243</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>539985; 718220</t>
+          <t>541013; 715360</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2055957; 2216426</t>
+          <t>2058038; 2217789</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2134504; 2306492</t>
+          <t>2135898; 2294663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2011008; 2158537</t>
+          <t>1998494; 2159290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1283543; 1605420</t>
+          <t>1283051; 1598379</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,21; 37,03</t>
+          <t>31,08; 37,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 35,3</t>
+          <t>29,02; 35,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,51; 32,99</t>
+          <t>26,89; 33,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 31,45</t>
+          <t>22,93; 30,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,85</t>
+          <t>11,33; 14,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 16,63</t>
+          <t>12,89; 16,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 16,12</t>
+          <t>11,77; 16,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,18</t>
+          <t>8,8; 12,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,66; 24,1</t>
+          <t>20,64; 24,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,31; 23,81</t>
+          <t>20,35; 23,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,55; 22,59</t>
+          <t>18,87; 22,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 19,21</t>
+          <t>15,38; 19,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,91; 47,94</t>
+          <t>42,87; 47,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,12; 42,38</t>
+          <t>37,91; 42,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,65; 41,08</t>
+          <t>36,66; 40,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,81; 29,69</t>
+          <t>26,21; 30,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 35,79</t>
+          <t>31,06; 35,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,22; 38,2</t>
+          <t>33,43; 37,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 35,31</t>
+          <t>31,2; 35,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,75; 24,02</t>
+          <t>21,44; 25,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,94; 41,34</t>
+          <t>37,81; 41,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,46; 39,6</t>
+          <t>36,4; 39,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,62; 37,69</t>
+          <t>34,65; 37,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 26,26</t>
+          <t>24,63; 27,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 38,05</t>
+          <t>29,63; 37,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,6; 37,6</t>
+          <t>28,32; 37,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 29,05</t>
+          <t>21,13; 29,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,58</t>
+          <t>12,59; 18,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,79; 30,63</t>
+          <t>23,09; 30,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,43; 34,53</t>
+          <t>25,35; 34,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 25,55</t>
+          <t>18,88; 26,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 19,05</t>
+          <t>13,75; 19,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 33,31</t>
+          <t>27,54; 32,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,59; 34,18</t>
+          <t>28,02; 34,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 26,35</t>
+          <t>20,95; 26,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 18,67</t>
+          <t>13,83; 17,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,25; 41,68</t>
+          <t>38,16; 41,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,1; 38,46</t>
+          <t>35,1; 38,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,9; 36,19</t>
+          <t>32,72; 36,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,56</t>
+          <t>24,05; 27,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,11; 25,95</t>
+          <t>23,14; 26,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 28,57</t>
+          <t>25,41; 28,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 27,51</t>
+          <t>24,35; 27,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,6</t>
+          <t>17,84; 20,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,93; 33,33</t>
+          <t>30,98; 33,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,64; 32,92</t>
+          <t>30,64; 32,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 31,28</t>
+          <t>29,16; 31,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,07; 22,51</t>
+          <t>21,24; 23,16</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141171</t>
+          <t>152480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>86165</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>220016</t>
+          <t>238645</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>321721; 381632</t>
+          <t>320333; 384935</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>285881; 344073</t>
+          <t>282838; 341297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199745; 248570</t>
+          <t>202646; 253421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120868; 161940</t>
+          <t>132685; 175282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>147783; 195295</t>
+          <t>148967; 196911</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>170834; 222476</t>
+          <t>172410; 224835</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>114211; 159950</t>
+          <t>116831; 160636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67092; 91988</t>
+          <t>72315; 100676</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>484580; 565242</t>
+          <t>484206; 564289</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>469586; 550576</t>
+          <t>470571; 549985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>323901; 394300</t>
+          <t>329426; 396559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>196478; 244067</t>
+          <t>215422; 267387</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589277</t>
+          <t>638318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>464472</t>
+          <t>502270</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1053749</t>
+          <t>1140589</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>726712; 811865</t>
+          <t>725920; 805834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>748262; 831825</t>
+          <t>744102; 834579</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>761085; 853057</t>
+          <t>761109; 848937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>430492; 679356</t>
+          <t>583978; 688518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>495661; 568206</t>
+          <t>493098; 566712</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>583198; 670806</t>
+          <t>586930; 666905</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>618596; 701404</t>
+          <t>619601; 701153</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>352286; 537096</t>
+          <t>465232; 543218</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1244972; 1356350</t>
+          <t>1240447; 1354491</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1355763; 1472522</t>
+          <t>1353624; 1479661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1406342; 1531101</t>
+          <t>1407671; 1527795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>840496; 1188248</t>
+          <t>1083527; 1203043</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>110282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>107408</t>
+          <t>117389</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>210850</t>
+          <t>227671</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163797; 209809</t>
+          <t>163372; 207766</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>137596; 180937</t>
+          <t>136289; 178167</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115378; 158574</t>
+          <t>115355; 158343</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84075; 133102</t>
+          <t>89581; 130340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>108580; 145905</t>
+          <t>109991; 147299</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>116620; 158387</t>
+          <t>116253; 158675</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>101448; 140069</t>
+          <t>103477; 142606</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90574; 125348</t>
+          <t>100679; 139501</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>280573; 342402</t>
+          <t>283093; 338479</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259269; 321209</t>
+          <t>263380; 322061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>228087; 288264</t>
+          <t>229201; 285207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>186162; 243512</t>
+          <t>199708; 256975</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833890</t>
+          <t>901081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>650725</t>
+          <t>705824</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1484616</t>
+          <t>1606904</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1252736; 1365380</t>
+          <t>1249910; 1361442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1200043; 1314908</t>
+          <t>1200054; 1316732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1110754; 1221694</t>
+          <t>1104532; 1219393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>644246; 916288</t>
+          <t>846075; 959973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>781070; 876985</t>
+          <t>782094; 883362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>906191; 1014851</t>
+          <t>902563; 1015106</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>861760; 970243</t>
+          <t>858570; 972637</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>541013; 715360</t>
+          <t>664337; 749268</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2058038; 2217789</t>
+          <t>2061715; 2208510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2135898; 2294663</t>
+          <t>2135591; 2296540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1998494; 2159290</t>
+          <t>2012717; 2160256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1283051; 1598379</t>
+          <t>1538367; 1677482</t>
         </is>
       </c>
     </row>
